--- a/results/lendt_energy.xlsx
+++ b/results/lendt_energy.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Energy Expenditure" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Energy Expenditure matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -698,18 +699,24 @@
           <t>support_total</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
         <v>7205</v>
       </c>
       <c r="D8" t="n">
         <v>24609</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
         <v>116934</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" t="n">
         <v>107635</v>
       </c>
@@ -723,18 +730,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>20</v>
       </c>
       <c r="D9" t="n">
         <v>69</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" t="n">
         <v>69</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="n">
         <v>68</v>
       </c>
@@ -748,23 +761,1410 @@
           <t>n_total</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>69</v>
+      </c>
       <c r="C10" t="n">
         <v>69</v>
       </c>
       <c r="D10" t="n">
         <v>69</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>69</v>
+      </c>
       <c r="F10" t="n">
         <v>69</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>69</v>
+      </c>
       <c r="H10" t="n">
         <v>69</v>
       </c>
       <c r="I10" t="n">
         <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.51024935568834</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9770807593182821</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0627092678546106</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9615421635669685</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9926193550695956</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>69</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D5" t="n">
+        <v>69</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1547331473711531</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.002380509959556201</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.009339748274720443</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.623365200337378e-05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.004694786267109029</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1469766278834321</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.002261178890514341</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.00319347686932292</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.001469874067300224</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.003052483713728457</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>69</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.10086898515463</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01693644592545585</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0488586539090788</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.004829864266638185</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0290430275842735</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>69</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.08717188390245266</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001341105906191579</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.009193647000510721</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.003619180090575626</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>68</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>68</v>
+      </c>
+      <c r="D11" t="n">
+        <v>69</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.029989437863065</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01514690349798624</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05806957913274655</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001091070881967382</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0292027361140051</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>68</v>
+      </c>
+      <c r="D12" t="n">
+        <v>69</v>
+      </c>
+      <c r="E12" t="n">
+        <v>66.03975672463828</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9711728930093865</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05783904388820978</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9571728618105243</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9851729242082486</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>68</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2729812199307489</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.004014429704863954</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.004136114372114751</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.003013276740378792</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.005015582669349115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>68</v>
+      </c>
+      <c r="D14" t="n">
+        <v>69</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>68</v>
+      </c>
+      <c r="D15" t="n">
+        <v>69</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>68</v>
+      </c>
+      <c r="D16" t="n">
+        <v>69</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2340361852608154</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.003441708606776697</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001752841699765567</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.003017430526889785</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.003865986686663608</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>68</v>
+      </c>
+      <c r="D17" t="n">
+        <v>69</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4232364323070822</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.006224065180986503</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.00532664384621287</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.004934742691902125</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.007513387670070881</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>69</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>69</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4442616583193193</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.04207914368655463</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4579208563134454</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>69</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>69</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>69</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4442616583193193</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5420791436865546</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9579208563134454</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>69</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>69</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>69</v>
+      </c>
+      <c r="D26" t="n">
+        <v>69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>69</v>
+      </c>
+      <c r="D27" t="n">
+        <v>69</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>69</v>
+      </c>
+      <c r="D28" t="n">
+        <v>69</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>69</v>
+      </c>
+      <c r="D29" t="n">
+        <v>69</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.176923076923077</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.01705685618729097</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.03159338485095734</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00946729646372781</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.02464641591085413</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>69</v>
+      </c>
+      <c r="D30" t="n">
+        <v>69</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>69</v>
+      </c>
+      <c r="D31" t="n">
+        <v>69</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>69</v>
+      </c>
+      <c r="D32" t="n">
+        <v>69</v>
+      </c>
+      <c r="E32" t="n">
+        <v>67.82307692307693</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9829431438127091</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.03159338485095735</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.975353584089146</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9905327035362722</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>69</v>
+      </c>
+      <c r="D33" t="n">
+        <v>69</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>69</v>
+      </c>
+      <c r="D34" t="n">
+        <v>69</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>69</v>
+      </c>
+      <c r="D35" t="n">
+        <v>69</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>69</v>
+      </c>
+      <c r="D36" t="n">
+        <v>69</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.06022403968132214</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0008728121692945238</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.006718889579256156</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.00248686568012768</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>69</v>
+      </c>
+      <c r="D37" t="n">
+        <v>69</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.104384001735613</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.01600556524254512</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.03243411112815306</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.008214041015271855</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.02379708946981838</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>69</v>
+      </c>
+      <c r="D38" t="n">
+        <v>69</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.004441976679622432</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.437647361771641e-05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.000534751151963439</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0001928377266368825</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>69</v>
+      </c>
+      <c r="D39" t="n">
+        <v>69</v>
+      </c>
+      <c r="E39" t="n">
+        <v>15.96521040972242</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.2313798610104698</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4010581880767003</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1350351646320472</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3277245573888925</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>69</v>
+      </c>
+      <c r="D40" t="n">
+        <v>69</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9257363201515386</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.01341646840799331</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.04885906405160689</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.001679239668293024</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0251536971476936</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>69</v>
+      </c>
+      <c r="D41" t="n">
+        <v>69</v>
+      </c>
+      <c r="E41" t="n">
+        <v>50.94000325202948</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.7382609166960795</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.3998215054254021</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6422133039282102</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8343085294639488</v>
       </c>
     </row>
   </sheetData>

--- a/results/lendt_energy.xlsx
+++ b/results/lendt_energy.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,20 +440,30 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>stairs</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>run</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bicycle</t>
         </is>
@@ -467,42 +477,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89 [0.86, 0.92]</t>
+          <t>0.95 [0.94, 0.96]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.95 [0.94, 0.96]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.95 [0.94, 0.96]</t>
         </is>
       </c>
     </row>
@@ -520,24 +540,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.93 [0.91, 0.96]</t>
+          <t>0.97 [0.97, 0.97]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.76 [0.66, 0.85]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.98 [0.98, 0.99]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.99 [0.98, 1.00]</t>
+          <t>0.92 [0.90, 0.94]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.74 [0.67, 0.81]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.99 [0.99, 0.99]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
     </row>
@@ -549,42 +575,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.93 [0.91, 0.94]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.93 [0.91, 0.94]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
     </row>
@@ -602,22 +638,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.91 [0.87, 0.94]</t>
+          <t>0.96 [0.95, 0.96]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.97 [0.94, 1.00]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+          <t>0.96 [0.94, 0.98]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.81 [0.75, 0.87]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1.00 [1.00, 1.00]</t>
         </is>
@@ -637,24 +679,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.98 [0.98, 0.99]</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.74 [0.64, 0.83]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.97 [0.96, 0.99]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.98 [0.96, 0.99]</t>
+          <t>0.90 [0.86, 0.93]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.82 [0.74, 0.90]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.99 [0.98, 0.99]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
     </row>
@@ -672,24 +720,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>356.65 ± 15.69</t>
+          <t>353.45 ± 30.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1694.70 ± 163.83</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1582.87 ± 258.25</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1569.45 ± 332.17</t>
+          <t>1324.93 ± 169.02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>360.43 ± 0.50</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1560.78 ± 285.01</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1536.18 ± 332.84</t>
         </is>
       </c>
     </row>
@@ -706,22 +760,28 @@
         <v>7205</v>
       </c>
       <c r="D8" t="n">
-        <v>24609</v>
+        <v>23681</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>116934</v>
+        <v>88770</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>24149</v>
       </c>
       <c r="H8" t="n">
-        <v>107635</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>102014</v>
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>106133</v>
+      </c>
+      <c r="K8" t="n">
+        <v>99852</v>
       </c>
     </row>
     <row r="9">
@@ -737,21 +797,27 @@
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>68</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>65</v>
       </c>
     </row>
@@ -783,6 +849,12 @@
         <v>69</v>
       </c>
       <c r="I10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J10" t="n">
+        <v>69</v>
+      </c>
+      <c r="K10" t="n">
         <v>69</v>
       </c>
     </row>
@@ -797,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,19 +937,19 @@
         <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>63.51024935568834</v>
+        <v>64.75602389537951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9770807593182821</v>
+        <v>0.9962465214673771</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0627092678546106</v>
+        <v>0.003006827353627396</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9615421635669685</v>
+        <v>0.9955014661296185</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9926193550695956</v>
+        <v>0.9969915768051357</v>
       </c>
     </row>
     <row r="3">
@@ -888,7 +960,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -921,7 +993,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -954,7 +1026,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -964,19 +1036,19 @@
         <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1547331473711531</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002380509959556201</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009339748274720443</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6.623365200337378e-05</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004694786267109029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -987,7 +1059,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -997,19 +1069,19 @@
         <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1469766278834321</v>
+        <v>0.0009250693802035153</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002261178890514341</v>
+        <v>1.423183661851562e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00319347686932292</v>
+        <v>0.0001147407350501466</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001469874067300224</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003052483713728457</v>
+        <v>4.266319866672871e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1020,7 +1092,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1030,19 +1102,19 @@
         <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.1275976004282059</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.001963040006587783</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.002457853771038875</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.001354013662147585</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.002572066351027981</v>
       </c>
     </row>
     <row r="8">
@@ -1053,7 +1125,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1063,19 +1135,19 @@
         <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>1.10086898515463</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01693644592545585</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0488586539090788</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004829864266638185</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0290430275842735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1086,7 +1158,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1096,85 +1168,85 @@
         <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08717188390245266</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001341105906191579</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009193647000510721</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003619180090575626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.115453434812086</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.001776206689416708</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.002241250585819906</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.001220851986325724</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.002331561392507692</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D11" t="n">
         <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>1.029989437863065</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01514690349798624</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05806957913274655</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001091070881967382</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0292027361140051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1185,7 +1257,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1195,19 +1267,19 @@
         <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>66.03975672463828</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9711728930093865</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05783904388820978</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9571728618105243</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9851729242082486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1218,7 +1290,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1228,19 +1300,19 @@
         <v>69</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2729812199307489</v>
+        <v>0.4755333157347715</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004014429704863954</v>
+        <v>0.006993136996099581</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004136114372114751</v>
+        <v>0.003134059662667531</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003013276740378792</v>
+        <v>0.006234532944116196</v>
       </c>
       <c r="I13" t="n">
-        <v>0.005015582669349115</v>
+        <v>0.007751741048082966</v>
       </c>
     </row>
     <row r="14">
@@ -1251,7 +1323,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1284,7 +1356,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1294,19 +1366,19 @@
         <v>69</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>67.02257008748339</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.9856260306982851</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.00329773690665924</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.9848278083129341</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.9864242530836361</v>
       </c>
     </row>
     <row r="16">
@@ -1317,7 +1389,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1327,19 +1399,19 @@
         <v>69</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2340361852608154</v>
+        <v>0.1510436912306513</v>
       </c>
       <c r="F16" t="n">
-        <v>0.003441708606776697</v>
+        <v>0.002221230753391932</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001752841699765567</v>
+        <v>0.002714619127076381</v>
       </c>
       <c r="H16" t="n">
-        <v>0.003017430526889785</v>
+        <v>0.001564152940253248</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003865986686663608</v>
+        <v>0.002878308566530615</v>
       </c>
     </row>
     <row r="17">
@@ -1350,7 +1422,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1360,151 +1432,151 @@
         <v>69</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4232364323070822</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006224065180986503</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00532664384621287</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.004934742691902125</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.007513387670070881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D18" t="n">
         <v>69</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.07564892235739104</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.001112484152314574</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.001238419361523648</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.0008127228054272297</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.001412245499201918</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
         <v>69</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4442616583193193</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04207914368655463</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4579208563134454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D20" t="n">
         <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.2426826791412801</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.003568862928548236</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.001638954173758008</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.003172151502777335</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.003965574354319137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
         <v>69</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.03252130405251943</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.0004782544713605799</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.0007420481662876678</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.0002986405500245899</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.00065786839269657</v>
       </c>
     </row>
     <row r="22">
@@ -1515,7 +1587,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1525,19 +1597,19 @@
         <v>69</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4442616583193193</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5420791436865546</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9579208563134454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1548,7 +1620,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1581,7 +1653,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1591,19 +1663,19 @@
         <v>69</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.4442616583193193</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.04207914368655463</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.4579208563134454</v>
       </c>
     </row>
     <row r="25">
@@ -1614,7 +1686,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1642,16 +1714,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D26" t="n">
         <v>69</v>
@@ -1675,49 +1747,49 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D27" t="n">
         <v>69</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.4442616583193193</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.5420791436865546</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.9579208563134454</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
         <v>69</v>
@@ -1741,49 +1813,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
         <v>69</v>
       </c>
       <c r="E29" t="n">
-        <v>1.176923076923077</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01705685618729097</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03159338485095734</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00946729646372781</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02464641591085413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>stand</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sit</t>
-        </is>
-      </c>
       <c r="C30" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
         <v>69</v>
@@ -1807,16 +1879,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D31" t="n">
         <v>69</v>
@@ -1840,82 +1912,82 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D32" t="n">
         <v>69</v>
       </c>
       <c r="E32" t="n">
-        <v>67.82307692307693</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9829431438127091</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.03159338485095735</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.975353584089146</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9905327035362722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>fast-walk</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D33" t="n">
         <v>69</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.006245181484194305</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>9.321166394319858e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.000538828021467175</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.0002246421453871568</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D34" t="n">
         <v>69</v>
@@ -1939,16 +2011,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D35" t="n">
         <v>69</v>
@@ -1972,106 +2044,106 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>shuffle</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D36" t="n">
         <v>69</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06022403968132214</v>
+        <v>0.7718052101804176</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0008728121692945238</v>
+        <v>0.01151948074896146</v>
       </c>
       <c r="G36" t="n">
-        <v>0.006718889579256156</v>
+        <v>0.03841129956080175</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.00215022860721511</v>
       </c>
       <c r="I36" t="n">
-        <v>0.00248686568012768</v>
+        <v>0.0208887328907078</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>sit</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D37" t="n">
         <v>69</v>
       </c>
       <c r="E37" t="n">
-        <v>1.104384001735613</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01600556524254512</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.03243411112815306</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.008214041015271855</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02379708946981838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D38" t="n">
         <v>69</v>
       </c>
       <c r="E38" t="n">
-        <v>0.004441976679622432</v>
+        <v>60.13182899508313</v>
       </c>
       <c r="F38" t="n">
-        <v>6.437647361771641e-05</v>
+        <v>0.8974899850012407</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000534751151963439</v>
+        <v>0.1345431490385895</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.8646723323391189</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0001928377266368825</v>
+        <v>0.9303076376633624</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2080,31 +2152,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D39" t="n">
         <v>69</v>
       </c>
       <c r="E39" t="n">
-        <v>15.96521040972242</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2313798610104698</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4010581880767003</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1350351646320472</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3277245573888925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>slow-walk</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2113,58 +2185,718 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D40" t="n">
         <v>69</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9257363201515386</v>
+        <v>0.298792246929334</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01341646840799331</v>
+        <v>0.004459585775064686</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04885906405160689</v>
+        <v>0.001954796195209753</v>
       </c>
       <c r="H40" t="n">
-        <v>0.001679239668293024</v>
+        <v>0.003982773518044963</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0251536971476936</v>
+        <v>0.00493639803208441</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="n">
+        <v>67</v>
+      </c>
+      <c r="D41" t="n">
+        <v>69</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5.79132836632293</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.08643773681079001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1337664750656366</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.05380952981616014</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1190659438054199</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>67</v>
+      </c>
+      <c r="D42" t="n">
+        <v>69</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>67</v>
+      </c>
+      <c r="D43" t="n">
+        <v>69</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>67</v>
+      </c>
+      <c r="D44" t="n">
+        <v>69</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>67</v>
+      </c>
+      <c r="D45" t="n">
+        <v>69</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>67</v>
+      </c>
+      <c r="D46" t="n">
+        <v>69</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.183176100628931</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.01765934478550642</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.03198819984099972</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.009856809768525578</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.02546187980248727</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>67</v>
+      </c>
+      <c r="D47" t="n">
+        <v>69</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>67</v>
+      </c>
+      <c r="D48" t="n">
+        <v>69</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>67</v>
+      </c>
+      <c r="D49" t="n">
+        <v>69</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>69</v>
+      </c>
+      <c r="E50" t="n">
+        <v>65.81682389937107</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9823406552144937</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.03198819984099973</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.9745381201975128</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9901431902314745</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>walk</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>69</v>
-      </c>
-      <c r="D41" t="n">
-        <v>69</v>
-      </c>
-      <c r="E41" t="n">
-        <v>50.94000325202948</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.7382609166960795</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.3998215054254021</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.6422133039282102</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.8343085294639488</v>
+      <c r="C51" t="n">
+        <v>67</v>
+      </c>
+      <c r="D51" t="n">
+        <v>69</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>67</v>
+      </c>
+      <c r="D52" t="n">
+        <v>69</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fast-walk</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>67</v>
+      </c>
+      <c r="D53" t="n">
+        <v>69</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8615804863034779</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.01285941024333549</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.06686503468094777</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.02916907371620908</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>67</v>
+      </c>
+      <c r="D54" t="n">
+        <v>69</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>67</v>
+      </c>
+      <c r="D55" t="n">
+        <v>69</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>67</v>
+      </c>
+      <c r="D56" t="n">
+        <v>69</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.04993074792243768</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0007452350436184728</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.001843598445787623</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.0002955460488638424</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.001194924038373103</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>67</v>
+      </c>
+      <c r="D57" t="n">
+        <v>69</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>slow-walk</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>67</v>
+      </c>
+      <c r="D58" t="n">
+        <v>69</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.74632194521392</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.1603928648539391</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.3191617613840513</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.08254319429859472</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.2382425354092834</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>67</v>
+      </c>
+      <c r="D59" t="n">
+        <v>69</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.05277777777777778</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0007877280265339967</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.006447831785471665</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.002360477776123297</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>67</v>
+      </c>
+      <c r="D60" t="n">
+        <v>69</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2774930747922437</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.004141687683466324</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.002791384799235363</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.003460815432131118</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.00482255993480153</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>67</v>
+      </c>
+      <c r="D61" t="n">
+        <v>69</v>
+      </c>
+      <c r="E61" t="n">
+        <v>55.01189596799014</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.8210730741491066</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.3200321793463251</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7430110919706072</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8991350563276059</v>
       </c>
     </row>
   </sheetData>
